--- a/ieee_submission/Supplementary_ML-BMS-Corpus.xlsx
+++ b/ieee_submission/Supplementary_ML-BMS-Corpus.xlsx
@@ -31,34 +31,37 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Noto Sans CJK SC"/>
-      <color rgb="001B2A4A"/>
-      <sz val="16"/>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001F4E79"/>
+      <sz val="14"/>
     </font>
     <font>
-      <name val="Noto Sans CJK SC"/>
+      <name val="Calibri"/>
+      <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="11"/>
+      <sz val="10"/>
     </font>
     <font>
-      <name val="Noto Sans CJK SC"/>
-      <color rgb="0037352F"/>
-      <sz val="11"/>
+      <name val="Calibri"/>
+      <sz val="9"/>
     </font>
     <font>
-      <name val="Noto Sans CJK SC"/>
-      <color rgb="001B2A4A"/>
+      <name val="Calibri"/>
+      <color rgb="000563C1"/>
       <sz val="10"/>
       <u val="single"/>
     </font>
     <font>
-      <name val="Noto Sans CJK SC"/>
-      <color rgb="008C8A84"/>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="00595959"/>
       <sz val="9"/>
     </font>
     <font>
-      <name val="Noto Sans CJK SC"/>
-      <color rgb="001B2A4A"/>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001F4E79"/>
       <sz val="11"/>
     </font>
   </fonts>
@@ -71,7 +74,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001B2A4A"/>
+        <fgColor rgb="001F4E79"/>
       </patternFill>
     </fill>
     <fill>
@@ -81,7 +84,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F7F7F5"/>
+        <fgColor rgb="00F2F6FA"/>
       </patternFill>
     </fill>
   </fills>
@@ -94,8 +97,17 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="00B0B0B0"/>
+      </left>
+      <right style="thin">
+        <color rgb="00B0B0B0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B0B0B0"/>
+      </top>
       <bottom style="thin">
-        <color rgb="00E9E9E8"/>
+        <color rgb="00B0B0B0"/>
       </bottom>
     </border>
   </borders>
@@ -104,29 +116,27 @@
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -495,37 +505,34 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P109"/>
+  <dimension ref="B2:P109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="3" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
     <col width="46" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
     <col width="26" customWidth="1" min="6" max="6"/>
     <col width="30" customWidth="1" min="7" max="7"/>
-    <col width="38" customWidth="1" min="8" max="8"/>
+    <col width="39" customWidth="1" min="8" max="8"/>
     <col width="22" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
     <col width="15" customWidth="1" min="12" max="12"/>
-    <col width="37" customWidth="1" min="13" max="13"/>
-    <col width="8" customWidth="1" min="14" max="14"/>
+    <col width="38" customWidth="1" min="13" max="13"/>
+    <col width="11" customWidth="1" min="14" max="14"/>
     <col width="42" customWidth="1" min="15" max="15"/>
     <col width="40" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1"/>
-    <row r="2" ht="32" customHeight="1">
+    <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
           <t>Machine Learning in Battery Management Systems — Verified Corpus (103 papers, 2019–2026)</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="8" customHeight="1"/>
-    <row r="4" ht="38" customHeight="1">
+    <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
           <t>#</t>
@@ -602,7 +609,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="70" customHeight="1">
+    <row r="5" ht="14" customHeight="1">
       <c r="B5" s="3" t="n">
         <v>1</v>
       </c>
@@ -673,7 +680,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="70" customHeight="1">
+    <row r="6" ht="14" customHeight="1">
       <c r="B6" s="6" t="n">
         <v>2</v>
       </c>
@@ -744,7 +751,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="70" customHeight="1">
+    <row r="7" ht="14" customHeight="1">
       <c r="B7" s="3" t="n">
         <v>3</v>
       </c>
@@ -815,7 +822,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="54" customHeight="1">
+    <row r="8" ht="14" customHeight="1">
       <c r="B8" s="6" t="n">
         <v>4</v>
       </c>
@@ -886,7 +893,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="54" customHeight="1">
+    <row r="9" ht="14" customHeight="1">
       <c r="B9" s="3" t="n">
         <v>5</v>
       </c>
@@ -957,7 +964,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="54" customHeight="1">
+    <row r="10" ht="14" customHeight="1">
       <c r="B10" s="6" t="n">
         <v>6</v>
       </c>
@@ -1011,7 +1018,7 @@
       </c>
       <c r="M10" s="7" t="inlineStr">
         <is>
-          <t>online/real-vehicle</t>
+          <t>experimental hardware</t>
         </is>
       </c>
       <c r="N10" s="6" t="n">
@@ -1028,7 +1035,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="70" customHeight="1">
+    <row r="11" ht="14" customHeight="1">
       <c r="B11" s="3" t="n">
         <v>7</v>
       </c>
@@ -1099,7 +1106,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="70" customHeight="1">
+    <row r="12" ht="14" customHeight="1">
       <c r="B12" s="6" t="n">
         <v>8</v>
       </c>
@@ -1170,7 +1177,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="54" customHeight="1">
+    <row r="13" ht="14" customHeight="1">
       <c r="B13" s="3" t="n">
         <v>9</v>
       </c>
@@ -1241,7 +1248,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="70" customHeight="1">
+    <row r="14" ht="14" customHeight="1">
       <c r="B14" s="6" t="n">
         <v>10</v>
       </c>
@@ -1312,7 +1319,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="54" customHeight="1">
+    <row r="15" ht="14" customHeight="1">
       <c r="B15" s="3" t="n">
         <v>11</v>
       </c>
@@ -1383,7 +1390,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="70" customHeight="1">
+    <row r="16" ht="14" customHeight="1">
       <c r="B16" s="6" t="n">
         <v>12</v>
       </c>
@@ -1454,7 +1461,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="54" customHeight="1">
+    <row r="17" ht="14" customHeight="1">
       <c r="B17" s="3" t="n">
         <v>13</v>
       </c>
@@ -1525,7 +1532,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="70" customHeight="1">
+    <row r="18" ht="14" customHeight="1">
       <c r="B18" s="6" t="n">
         <v>14</v>
       </c>
@@ -1596,7 +1603,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="54" customHeight="1">
+    <row r="19" ht="14" customHeight="1">
       <c r="B19" s="3" t="n">
         <v>15</v>
       </c>
@@ -1667,7 +1674,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="54" customHeight="1">
+    <row r="20" ht="14" customHeight="1">
       <c r="B20" s="6" t="n">
         <v>16</v>
       </c>
@@ -1738,7 +1745,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="54" customHeight="1">
+    <row r="21" ht="14" customHeight="1">
       <c r="B21" s="3" t="n">
         <v>17</v>
       </c>
@@ -1809,7 +1816,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="54" customHeight="1">
+    <row r="22" ht="14" customHeight="1">
       <c r="B22" s="6" t="n">
         <v>18</v>
       </c>
@@ -1880,7 +1887,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="54" customHeight="1">
+    <row r="23" ht="14" customHeight="1">
       <c r="B23" s="3" t="n">
         <v>19</v>
       </c>
@@ -1951,7 +1958,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="54" customHeight="1">
+    <row r="24" ht="14" customHeight="1">
       <c r="B24" s="6" t="n">
         <v>20</v>
       </c>
@@ -2022,7 +2029,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="70" customHeight="1">
+    <row r="25" ht="14" customHeight="1">
       <c r="B25" s="3" t="n">
         <v>21</v>
       </c>
@@ -2093,7 +2100,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="54" customHeight="1">
+    <row r="26" ht="14" customHeight="1">
       <c r="B26" s="6" t="n">
         <v>22</v>
       </c>
@@ -2164,7 +2171,7 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="54" customHeight="1">
+    <row r="27" ht="14" customHeight="1">
       <c r="B27" s="3" t="n">
         <v>23</v>
       </c>
@@ -2235,7 +2242,7 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="54" customHeight="1">
+    <row r="28" ht="14" customHeight="1">
       <c r="B28" s="6" t="n">
         <v>24</v>
       </c>
@@ -2306,7 +2313,7 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="54" customHeight="1">
+    <row r="29" ht="14" customHeight="1">
       <c r="B29" s="3" t="n">
         <v>25</v>
       </c>
@@ -2377,7 +2384,7 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="54" customHeight="1">
+    <row r="30" ht="14" customHeight="1">
       <c r="B30" s="6" t="n">
         <v>26</v>
       </c>
@@ -2448,7 +2455,7 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="54" customHeight="1">
+    <row r="31" ht="14" customHeight="1">
       <c r="B31" s="3" t="n">
         <v>27</v>
       </c>
@@ -2519,7 +2526,7 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="70" customHeight="1">
+    <row r="32" ht="14" customHeight="1">
       <c r="B32" s="6" t="n">
         <v>28</v>
       </c>
@@ -2590,7 +2597,7 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="70" customHeight="1">
+    <row r="33" ht="14" customHeight="1">
       <c r="B33" s="3" t="n">
         <v>29</v>
       </c>
@@ -2661,7 +2668,7 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="54" customHeight="1">
+    <row r="34" ht="14" customHeight="1">
       <c r="B34" s="6" t="n">
         <v>30</v>
       </c>
@@ -2732,7 +2739,7 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="54" customHeight="1">
+    <row r="35" ht="14" customHeight="1">
       <c r="B35" s="3" t="n">
         <v>31</v>
       </c>
@@ -2803,7 +2810,7 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="54" customHeight="1">
+    <row r="36" ht="14" customHeight="1">
       <c r="B36" s="6" t="n">
         <v>32</v>
       </c>
@@ -2874,7 +2881,7 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="54" customHeight="1">
+    <row r="37" ht="14" customHeight="1">
       <c r="B37" s="3" t="n">
         <v>33</v>
       </c>
@@ -2945,7 +2952,7 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="54" customHeight="1">
+    <row r="38" ht="14" customHeight="1">
       <c r="B38" s="6" t="n">
         <v>34</v>
       </c>
@@ -3016,7 +3023,7 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="54" customHeight="1">
+    <row r="39" ht="14" customHeight="1">
       <c r="B39" s="3" t="n">
         <v>35</v>
       </c>
@@ -3087,7 +3094,7 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="54" customHeight="1">
+    <row r="40" ht="14" customHeight="1">
       <c r="B40" s="6" t="n">
         <v>36</v>
       </c>
@@ -3158,7 +3165,7 @@
         </is>
       </c>
     </row>
-    <row r="41" ht="70" customHeight="1">
+    <row r="41" ht="14" customHeight="1">
       <c r="B41" s="3" t="n">
         <v>37</v>
       </c>
@@ -3229,7 +3236,7 @@
         </is>
       </c>
     </row>
-    <row r="42" ht="70" customHeight="1">
+    <row r="42" ht="14" customHeight="1">
       <c r="B42" s="6" t="n">
         <v>38</v>
       </c>
@@ -3300,7 +3307,7 @@
         </is>
       </c>
     </row>
-    <row r="43" ht="54" customHeight="1">
+    <row r="43" ht="14" customHeight="1">
       <c r="B43" s="3" t="n">
         <v>39</v>
       </c>
@@ -3371,7 +3378,7 @@
         </is>
       </c>
     </row>
-    <row r="44" ht="54" customHeight="1">
+    <row r="44" ht="14" customHeight="1">
       <c r="B44" s="6" t="n">
         <v>40</v>
       </c>
@@ -3442,7 +3449,7 @@
         </is>
       </c>
     </row>
-    <row r="45" ht="54" customHeight="1">
+    <row r="45" ht="14" customHeight="1">
       <c r="B45" s="3" t="n">
         <v>41</v>
       </c>
@@ -3513,7 +3520,7 @@
         </is>
       </c>
     </row>
-    <row r="46" ht="54" customHeight="1">
+    <row r="46" ht="14" customHeight="1">
       <c r="B46" s="6" t="n">
         <v>42</v>
       </c>
@@ -3584,7 +3591,7 @@
         </is>
       </c>
     </row>
-    <row r="47" ht="54" customHeight="1">
+    <row r="47" ht="14" customHeight="1">
       <c r="B47" s="3" t="n">
         <v>43</v>
       </c>
@@ -3655,7 +3662,7 @@
         </is>
       </c>
     </row>
-    <row r="48" ht="70" customHeight="1">
+    <row r="48" ht="14" customHeight="1">
       <c r="B48" s="6" t="n">
         <v>44</v>
       </c>
@@ -3726,7 +3733,7 @@
         </is>
       </c>
     </row>
-    <row r="49" ht="54" customHeight="1">
+    <row r="49" ht="14" customHeight="1">
       <c r="B49" s="3" t="n">
         <v>45</v>
       </c>
@@ -3797,7 +3804,7 @@
         </is>
       </c>
     </row>
-    <row r="50" ht="70" customHeight="1">
+    <row r="50" ht="14" customHeight="1">
       <c r="B50" s="6" t="n">
         <v>46</v>
       </c>
@@ -3868,7 +3875,7 @@
         </is>
       </c>
     </row>
-    <row r="51" ht="70" customHeight="1">
+    <row r="51" ht="14" customHeight="1">
       <c r="B51" s="3" t="n">
         <v>47</v>
       </c>
@@ -3939,7 +3946,7 @@
         </is>
       </c>
     </row>
-    <row r="52" ht="54" customHeight="1">
+    <row r="52" ht="14" customHeight="1">
       <c r="B52" s="6" t="n">
         <v>48</v>
       </c>
@@ -4010,7 +4017,7 @@
         </is>
       </c>
     </row>
-    <row r="53" ht="54" customHeight="1">
+    <row r="53" ht="14" customHeight="1">
       <c r="B53" s="3" t="n">
         <v>49</v>
       </c>
@@ -4081,7 +4088,7 @@
         </is>
       </c>
     </row>
-    <row r="54" ht="54" customHeight="1">
+    <row r="54" ht="14" customHeight="1">
       <c r="B54" s="6" t="n">
         <v>50</v>
       </c>
@@ -4152,7 +4159,7 @@
         </is>
       </c>
     </row>
-    <row r="55" ht="54" customHeight="1">
+    <row r="55" ht="14" customHeight="1">
       <c r="B55" s="3" t="n">
         <v>51</v>
       </c>
@@ -4223,7 +4230,7 @@
         </is>
       </c>
     </row>
-    <row r="56" ht="70" customHeight="1">
+    <row r="56" ht="14" customHeight="1">
       <c r="B56" s="6" t="n">
         <v>52</v>
       </c>
@@ -4294,7 +4301,7 @@
         </is>
       </c>
     </row>
-    <row r="57" ht="70" customHeight="1">
+    <row r="57" ht="14" customHeight="1">
       <c r="B57" s="3" t="n">
         <v>53</v>
       </c>
@@ -4365,7 +4372,7 @@
         </is>
       </c>
     </row>
-    <row r="58" ht="70" customHeight="1">
+    <row r="58" ht="14" customHeight="1">
       <c r="B58" s="6" t="n">
         <v>54</v>
       </c>
@@ -4436,7 +4443,7 @@
         </is>
       </c>
     </row>
-    <row r="59" ht="70" customHeight="1">
+    <row r="59" ht="14" customHeight="1">
       <c r="B59" s="3" t="n">
         <v>55</v>
       </c>
@@ -4507,7 +4514,7 @@
         </is>
       </c>
     </row>
-    <row r="60" ht="54" customHeight="1">
+    <row r="60" ht="14" customHeight="1">
       <c r="B60" s="6" t="n">
         <v>56</v>
       </c>
@@ -4578,7 +4585,7 @@
         </is>
       </c>
     </row>
-    <row r="61" ht="70" customHeight="1">
+    <row r="61" ht="14" customHeight="1">
       <c r="B61" s="3" t="n">
         <v>57</v>
       </c>
@@ -4649,7 +4656,7 @@
         </is>
       </c>
     </row>
-    <row r="62" ht="70" customHeight="1">
+    <row r="62" ht="14" customHeight="1">
       <c r="B62" s="6" t="n">
         <v>58</v>
       </c>
@@ -4720,7 +4727,7 @@
         </is>
       </c>
     </row>
-    <row r="63" ht="70" customHeight="1">
+    <row r="63" ht="14" customHeight="1">
       <c r="B63" s="3" t="n">
         <v>59</v>
       </c>
@@ -4791,7 +4798,7 @@
         </is>
       </c>
     </row>
-    <row r="64" ht="70" customHeight="1">
+    <row r="64" ht="14" customHeight="1">
       <c r="B64" s="6" t="n">
         <v>60</v>
       </c>
@@ -4862,7 +4869,7 @@
         </is>
       </c>
     </row>
-    <row r="65" ht="70" customHeight="1">
+    <row r="65" ht="14" customHeight="1">
       <c r="B65" s="3" t="n">
         <v>61</v>
       </c>
@@ -4933,7 +4940,7 @@
         </is>
       </c>
     </row>
-    <row r="66" ht="70" customHeight="1">
+    <row r="66" ht="14" customHeight="1">
       <c r="B66" s="6" t="n">
         <v>62</v>
       </c>
@@ -5004,7 +5011,7 @@
         </is>
       </c>
     </row>
-    <row r="67" ht="54" customHeight="1">
+    <row r="67" ht="14" customHeight="1">
       <c r="B67" s="3" t="n">
         <v>63</v>
       </c>
@@ -5075,7 +5082,7 @@
         </is>
       </c>
     </row>
-    <row r="68" ht="54" customHeight="1">
+    <row r="68" ht="14" customHeight="1">
       <c r="B68" s="6" t="n">
         <v>64</v>
       </c>
@@ -5146,7 +5153,7 @@
         </is>
       </c>
     </row>
-    <row r="69" ht="70" customHeight="1">
+    <row r="69" ht="14" customHeight="1">
       <c r="B69" s="3" t="n">
         <v>65</v>
       </c>
@@ -5217,7 +5224,7 @@
         </is>
       </c>
     </row>
-    <row r="70" ht="54" customHeight="1">
+    <row r="70" ht="14" customHeight="1">
       <c r="B70" s="6" t="n">
         <v>66</v>
       </c>
@@ -5288,7 +5295,7 @@
         </is>
       </c>
     </row>
-    <row r="71" ht="70" customHeight="1">
+    <row r="71" ht="14" customHeight="1">
       <c r="B71" s="3" t="n">
         <v>67</v>
       </c>
@@ -5359,7 +5366,7 @@
         </is>
       </c>
     </row>
-    <row r="72" ht="54" customHeight="1">
+    <row r="72" ht="14" customHeight="1">
       <c r="B72" s="6" t="n">
         <v>68</v>
       </c>
@@ -5430,7 +5437,7 @@
         </is>
       </c>
     </row>
-    <row r="73" ht="54" customHeight="1">
+    <row r="73" ht="14" customHeight="1">
       <c r="B73" s="3" t="n">
         <v>69</v>
       </c>
@@ -5501,7 +5508,7 @@
         </is>
       </c>
     </row>
-    <row r="74" ht="70" customHeight="1">
+    <row r="74" ht="14" customHeight="1">
       <c r="B74" s="6" t="n">
         <v>70</v>
       </c>
@@ -5572,7 +5579,7 @@
         </is>
       </c>
     </row>
-    <row r="75" ht="70" customHeight="1">
+    <row r="75" ht="14" customHeight="1">
       <c r="B75" s="3" t="n">
         <v>71</v>
       </c>
@@ -5643,7 +5650,7 @@
         </is>
       </c>
     </row>
-    <row r="76" ht="54" customHeight="1">
+    <row r="76" ht="14" customHeight="1">
       <c r="B76" s="6" t="n">
         <v>72</v>
       </c>
@@ -5714,7 +5721,7 @@
         </is>
       </c>
     </row>
-    <row r="77" ht="54" customHeight="1">
+    <row r="77" ht="14" customHeight="1">
       <c r="B77" s="3" t="n">
         <v>73</v>
       </c>
@@ -5785,7 +5792,7 @@
         </is>
       </c>
     </row>
-    <row r="78" ht="54" customHeight="1">
+    <row r="78" ht="14" customHeight="1">
       <c r="B78" s="6" t="n">
         <v>74</v>
       </c>
@@ -5856,7 +5863,7 @@
         </is>
       </c>
     </row>
-    <row r="79" ht="70" customHeight="1">
+    <row r="79" ht="14" customHeight="1">
       <c r="B79" s="3" t="n">
         <v>75</v>
       </c>
@@ -5927,7 +5934,7 @@
         </is>
       </c>
     </row>
-    <row r="80" ht="54" customHeight="1">
+    <row r="80" ht="14" customHeight="1">
       <c r="B80" s="6" t="n">
         <v>76</v>
       </c>
@@ -5998,7 +6005,7 @@
         </is>
       </c>
     </row>
-    <row r="81" ht="54" customHeight="1">
+    <row r="81" ht="14" customHeight="1">
       <c r="B81" s="3" t="n">
         <v>77</v>
       </c>
@@ -6069,7 +6076,7 @@
         </is>
       </c>
     </row>
-    <row r="82" ht="54" customHeight="1">
+    <row r="82" ht="14" customHeight="1">
       <c r="B82" s="6" t="n">
         <v>78</v>
       </c>
@@ -6140,7 +6147,7 @@
         </is>
       </c>
     </row>
-    <row r="83" ht="70" customHeight="1">
+    <row r="83" ht="14" customHeight="1">
       <c r="B83" s="3" t="n">
         <v>79</v>
       </c>
@@ -6211,7 +6218,7 @@
         </is>
       </c>
     </row>
-    <row r="84" ht="54" customHeight="1">
+    <row r="84" ht="14" customHeight="1">
       <c r="B84" s="6" t="n">
         <v>80</v>
       </c>
@@ -6282,7 +6289,7 @@
         </is>
       </c>
     </row>
-    <row r="85" ht="54" customHeight="1">
+    <row r="85" ht="14" customHeight="1">
       <c r="B85" s="3" t="n">
         <v>81</v>
       </c>
@@ -6353,7 +6360,7 @@
         </is>
       </c>
     </row>
-    <row r="86" ht="54" customHeight="1">
+    <row r="86" ht="14" customHeight="1">
       <c r="B86" s="6" t="n">
         <v>82</v>
       </c>
@@ -6424,7 +6431,7 @@
         </is>
       </c>
     </row>
-    <row r="87" ht="54" customHeight="1">
+    <row r="87" ht="14" customHeight="1">
       <c r="B87" s="3" t="n">
         <v>83</v>
       </c>
@@ -6495,7 +6502,7 @@
         </is>
       </c>
     </row>
-    <row r="88" ht="54" customHeight="1">
+    <row r="88" ht="14" customHeight="1">
       <c r="B88" s="6" t="n">
         <v>84</v>
       </c>
@@ -6566,7 +6573,7 @@
         </is>
       </c>
     </row>
-    <row r="89" ht="38" customHeight="1">
+    <row r="89" ht="14" customHeight="1">
       <c r="B89" s="3" t="n">
         <v>85</v>
       </c>
@@ -6637,7 +6644,7 @@
         </is>
       </c>
     </row>
-    <row r="90" ht="86" customHeight="1">
+    <row r="90" ht="14" customHeight="1">
       <c r="B90" s="6" t="n">
         <v>86</v>
       </c>
@@ -6708,7 +6715,7 @@
         </is>
       </c>
     </row>
-    <row r="91" ht="54" customHeight="1">
+    <row r="91" ht="14" customHeight="1">
       <c r="B91" s="3" t="n">
         <v>87</v>
       </c>
@@ -6779,7 +6786,7 @@
         </is>
       </c>
     </row>
-    <row r="92" ht="70" customHeight="1">
+    <row r="92" ht="14" customHeight="1">
       <c r="B92" s="6" t="n">
         <v>88</v>
       </c>
@@ -6850,7 +6857,7 @@
         </is>
       </c>
     </row>
-    <row r="93" ht="54" customHeight="1">
+    <row r="93" ht="14" customHeight="1">
       <c r="B93" s="3" t="n">
         <v>89</v>
       </c>
@@ -6921,7 +6928,7 @@
         </is>
       </c>
     </row>
-    <row r="94" ht="54" customHeight="1">
+    <row r="94" ht="14" customHeight="1">
       <c r="B94" s="6" t="n">
         <v>90</v>
       </c>
@@ -6992,7 +6999,7 @@
         </is>
       </c>
     </row>
-    <row r="95" ht="70" customHeight="1">
+    <row r="95" ht="14" customHeight="1">
       <c r="B95" s="3" t="n">
         <v>91</v>
       </c>
@@ -7063,7 +7070,7 @@
         </is>
       </c>
     </row>
-    <row r="96" ht="70" customHeight="1">
+    <row r="96" ht="14" customHeight="1">
       <c r="B96" s="6" t="n">
         <v>92</v>
       </c>
@@ -7134,7 +7141,7 @@
         </is>
       </c>
     </row>
-    <row r="97" ht="54" customHeight="1">
+    <row r="97" ht="14" customHeight="1">
       <c r="B97" s="3" t="n">
         <v>93</v>
       </c>
@@ -7205,7 +7212,7 @@
         </is>
       </c>
     </row>
-    <row r="98" ht="54" customHeight="1">
+    <row r="98" ht="14" customHeight="1">
       <c r="B98" s="6" t="n">
         <v>94</v>
       </c>
@@ -7276,7 +7283,7 @@
         </is>
       </c>
     </row>
-    <row r="99" ht="54" customHeight="1">
+    <row r="99" ht="14" customHeight="1">
       <c r="B99" s="3" t="n">
         <v>95</v>
       </c>
@@ -7347,7 +7354,7 @@
         </is>
       </c>
     </row>
-    <row r="100" ht="70" customHeight="1">
+    <row r="100" ht="14" customHeight="1">
       <c r="B100" s="6" t="n">
         <v>96</v>
       </c>
@@ -7418,7 +7425,7 @@
         </is>
       </c>
     </row>
-    <row r="101" ht="54" customHeight="1">
+    <row r="101" ht="14" customHeight="1">
       <c r="B101" s="3" t="n">
         <v>97</v>
       </c>
@@ -7489,7 +7496,7 @@
         </is>
       </c>
     </row>
-    <row r="102" ht="54" customHeight="1">
+    <row r="102" ht="14" customHeight="1">
       <c r="B102" s="6" t="n">
         <v>98</v>
       </c>
@@ -7560,7 +7567,7 @@
         </is>
       </c>
     </row>
-    <row r="103" ht="70" customHeight="1">
+    <row r="103" ht="14" customHeight="1">
       <c r="B103" s="3" t="n">
         <v>99</v>
       </c>
@@ -7631,7 +7638,7 @@
         </is>
       </c>
     </row>
-    <row r="104" ht="54" customHeight="1">
+    <row r="104" ht="14" customHeight="1">
       <c r="B104" s="6" t="n">
         <v>100</v>
       </c>
@@ -7702,7 +7709,7 @@
         </is>
       </c>
     </row>
-    <row r="105" ht="54" customHeight="1">
+    <row r="105" ht="14" customHeight="1">
       <c r="B105" s="3" t="n">
         <v>101</v>
       </c>
@@ -7773,7 +7780,7 @@
         </is>
       </c>
     </row>
-    <row r="106" ht="70" customHeight="1">
+    <row r="106" ht="14" customHeight="1">
       <c r="B106" s="6" t="n">
         <v>102</v>
       </c>
@@ -7844,7 +7851,7 @@
         </is>
       </c>
     </row>
-    <row r="107" ht="70" customHeight="1">
+    <row r="107" ht="14" customHeight="1">
       <c r="B107" s="3" t="n">
         <v>103</v>
       </c>
@@ -7924,9 +7931,8 @@
     </row>
   </sheetData>
   <autoFilter ref="B4:P107"/>
-  <mergeCells count="2">
+  <mergeCells count="1">
     <mergeCell ref="B109:J109"/>
-    <mergeCell ref="B2:P2"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId1"/>
@@ -8043,24 +8049,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D52"/>
+  <dimension ref="B2:C52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="33" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1"/>
-    <row r="2" ht="32" customHeight="1">
+    <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
           <t>Corpus Summary — 103 peer-reviewed studies</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="8" customHeight="1"/>
     <row r="4">
       <c r="B4" s="10" t="inlineStr">
         <is>
@@ -8068,7 +8070,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="28" customHeight="1">
+    <row r="5">
       <c r="B5" s="2" t="inlineStr">
         <is>
           <t>Category</t>
@@ -8080,7 +8082,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="22" customHeight="1">
+    <row r="6" ht="14" customHeight="1">
       <c r="B6" s="4" t="inlineStr">
         <is>
           <t>State estimation (SOC)</t>
@@ -8090,7 +8092,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" ht="22" customHeight="1">
+    <row r="7" ht="14" customHeight="1">
       <c r="B7" s="7" t="inlineStr">
         <is>
           <t>Health estimation (SOH)</t>
@@ -8100,7 +8102,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" ht="22" customHeight="1">
+    <row r="8" ht="14" customHeight="1">
       <c r="B8" s="4" t="inlineStr">
         <is>
           <t>Prognostics (RUL)</t>
@@ -8110,7 +8112,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" ht="22" customHeight="1">
+    <row r="9" ht="14" customHeight="1">
       <c r="B9" s="7" t="inlineStr">
         <is>
           <t>Charging control</t>
@@ -8120,7 +8122,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" ht="22" customHeight="1">
+    <row r="10" ht="14" customHeight="1">
       <c r="B10" s="4" t="inlineStr">
         <is>
           <t>Thermal management</t>
@@ -8130,7 +8132,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" ht="22" customHeight="1">
+    <row r="11" ht="14" customHeight="1">
       <c r="B11" s="7" t="inlineStr">
         <is>
           <t>Fault &amp; safety</t>
@@ -8140,7 +8142,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" ht="22" customHeight="1">
+    <row r="12" ht="14" customHeight="1">
       <c r="B12" s="4" t="inlineStr">
         <is>
           <t>Cell balancing &amp; ECM</t>
@@ -8150,7 +8152,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" ht="22" customHeight="1">
+    <row r="13" ht="14" customHeight="1">
       <c r="B13" s="7" t="inlineStr">
         <is>
           <t>Cross-cutting</t>
@@ -8160,15 +8162,15 @@
         <v>24</v>
       </c>
     </row>
-    <row r="14" ht="22" customHeight="1"/>
-    <row r="15" ht="22" customHeight="1">
+    <row r="14" ht="14" customHeight="1"/>
+    <row r="15" ht="14" customHeight="1">
       <c r="B15" s="10" t="inlineStr">
         <is>
           <t>By publication year</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="28" customHeight="1">
+    <row r="16" ht="14" customHeight="1">
       <c r="B16" s="2" t="inlineStr">
         <is>
           <t>Category</t>
@@ -8180,7 +8182,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="22" customHeight="1">
+    <row r="17" ht="14" customHeight="1">
       <c r="B17" s="4" t="n">
         <v>2019</v>
       </c>
@@ -8188,7 +8190,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" ht="22" customHeight="1">
+    <row r="18" ht="14" customHeight="1">
       <c r="B18" s="7" t="n">
         <v>2020</v>
       </c>
@@ -8196,7 +8198,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" ht="22" customHeight="1">
+    <row r="19" ht="14" customHeight="1">
       <c r="B19" s="4" t="n">
         <v>2021</v>
       </c>
@@ -8204,7 +8206,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="20" ht="22" customHeight="1">
+    <row r="20" ht="14" customHeight="1">
       <c r="B20" s="7" t="n">
         <v>2022</v>
       </c>
@@ -8212,7 +8214,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="21" ht="22" customHeight="1">
+    <row r="21" ht="14" customHeight="1">
       <c r="B21" s="4" t="n">
         <v>2023</v>
       </c>
@@ -8220,7 +8222,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="22" ht="22" customHeight="1">
+    <row r="22" ht="14" customHeight="1">
       <c r="B22" s="7" t="n">
         <v>2024</v>
       </c>
@@ -8228,7 +8230,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="23" ht="22" customHeight="1">
+    <row r="23" ht="14" customHeight="1">
       <c r="B23" s="4" t="n">
         <v>2025</v>
       </c>
@@ -8236,7 +8238,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="24" ht="22" customHeight="1">
+    <row r="24" ht="14" customHeight="1">
       <c r="B24" s="7" t="n">
         <v>2026</v>
       </c>
@@ -8244,15 +8246,15 @@
         <v>7</v>
       </c>
     </row>
-    <row r="25" ht="22" customHeight="1"/>
-    <row r="26" ht="22" customHeight="1">
+    <row r="25" ht="14" customHeight="1"/>
+    <row r="26" ht="14" customHeight="1">
       <c r="B26" s="10" t="inlineStr">
         <is>
           <t>By method family</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="28" customHeight="1">
+    <row r="27" ht="14" customHeight="1">
       <c r="B27" s="2" t="inlineStr">
         <is>
           <t>Category</t>
@@ -8264,7 +8266,7 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="22" customHeight="1">
+    <row r="28" ht="14" customHeight="1">
       <c r="B28" s="4" t="inlineStr">
         <is>
           <t>Shallow ML</t>
@@ -8274,7 +8276,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="29" ht="22" customHeight="1">
+    <row r="29" ht="14" customHeight="1">
       <c r="B29" s="7" t="inlineStr">
         <is>
           <t>Deep learning</t>
@@ -8284,7 +8286,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="30" ht="22" customHeight="1">
+    <row r="30" ht="14" customHeight="1">
       <c r="B30" s="4" t="inlineStr">
         <is>
           <t>Review / perspective</t>
@@ -8294,7 +8296,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="31" ht="22" customHeight="1">
+    <row r="31" ht="14" customHeight="1">
       <c r="B31" s="7" t="inlineStr">
         <is>
           <t>Physics-informed</t>
@@ -8304,7 +8306,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="32" ht="22" customHeight="1">
+    <row r="32" ht="14" customHeight="1">
       <c r="B32" s="4" t="inlineStr">
         <is>
           <t>Hybrid physics+ML</t>
@@ -8314,7 +8316,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="33" ht="38" customHeight="1">
+    <row r="33" ht="14" customHeight="1">
       <c r="B33" s="7" t="inlineStr">
         <is>
           <t>Optimization-augmented control</t>
@@ -8324,7 +8326,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="34" ht="22" customHeight="1">
+    <row r="34" ht="14" customHeight="1">
       <c r="B34" s="4" t="inlineStr">
         <is>
           <t>Transfer learning</t>
@@ -8334,7 +8336,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="35" ht="22" customHeight="1">
+    <row r="35" ht="14" customHeight="1">
       <c r="B35" s="7" t="inlineStr">
         <is>
           <t>Filter-based hybrid</t>
@@ -8344,7 +8346,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="36" ht="22" customHeight="1">
+    <row r="36" ht="14" customHeight="1">
       <c r="B36" s="4" t="inlineStr">
         <is>
           <t>Bayesian optimization</t>
@@ -8354,7 +8356,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="37" ht="22" customHeight="1">
+    <row r="37" ht="14" customHeight="1">
       <c r="B37" s="7" t="inlineStr">
         <is>
           <t>Meta-heuristic-optimized DL</t>
@@ -8364,7 +8366,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="38" ht="22" customHeight="1">
+    <row r="38" ht="14" customHeight="1">
       <c r="B38" s="4" t="inlineStr">
         <is>
           <t>Foundation model / LLM</t>
@@ -8374,7 +8376,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="39" ht="22" customHeight="1">
+    <row r="39" ht="14" customHeight="1">
       <c r="B39" s="7" t="inlineStr">
         <is>
           <t>Reinforcement learning</t>
@@ -8384,7 +8386,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" ht="22" customHeight="1">
+    <row r="40" ht="14" customHeight="1">
       <c r="B40" s="4" t="inlineStr">
         <is>
           <t>Graph neural network</t>
@@ -8394,15 +8396,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" ht="22" customHeight="1"/>
-    <row r="42" ht="22" customHeight="1">
+    <row r="41" ht="14" customHeight="1"/>
+    <row r="42" ht="14" customHeight="1">
       <c r="B42" s="10" t="inlineStr">
         <is>
           <t>By primary data source</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="28" customHeight="1">
+    <row r="43" ht="14" customHeight="1">
       <c r="B43" s="2" t="inlineStr">
         <is>
           <t>Category</t>
@@ -8414,7 +8416,7 @@
         </is>
       </c>
     </row>
-    <row r="44" ht="22" customHeight="1">
+    <row r="44" ht="14" customHeight="1">
       <c r="B44" s="4" t="inlineStr">
         <is>
           <t>self-lab</t>
@@ -8424,7 +8426,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="45" ht="22" customHeight="1">
+    <row r="45" ht="14" customHeight="1">
       <c r="B45" s="7" t="inlineStr">
         <is>
           <t>review</t>
@@ -8434,7 +8436,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="46" ht="22" customHeight="1">
+    <row r="46" ht="14" customHeight="1">
       <c r="B46" s="4" t="inlineStr">
         <is>
           <t>simulation</t>
@@ -8444,7 +8446,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="47" ht="22" customHeight="1">
+    <row r="47" ht="14" customHeight="1">
       <c r="B47" s="7" t="inlineStr">
         <is>
           <t>Severson-MATR</t>
@@ -8454,7 +8456,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="48" ht="22" customHeight="1">
+    <row r="48" ht="14" customHeight="1">
       <c r="B48" s="4" t="inlineStr">
         <is>
           <t>real-vehicle</t>
@@ -8464,7 +8466,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="49" ht="22" customHeight="1">
+    <row r="49" ht="14" customHeight="1">
       <c r="B49" s="7" t="inlineStr">
         <is>
           <t>CALCE</t>
@@ -8474,7 +8476,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="50" ht="22" customHeight="1">
+    <row r="50" ht="14" customHeight="1">
       <c r="B50" s="4" t="inlineStr">
         <is>
           <t>EIS-lab</t>
@@ -8484,7 +8486,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="51" ht="22" customHeight="1">
+    <row r="51" ht="14" customHeight="1">
       <c r="B51" s="7" t="inlineStr">
         <is>
           <t>NASA</t>
@@ -8494,7 +8496,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="52" ht="22" customHeight="1">
+    <row r="52" ht="14" customHeight="1">
       <c r="B52" s="4" t="inlineStr">
         <is>
           <t>mixed</t>
@@ -8505,9 +8507,6 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B2:D2"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8518,32 +8517,29 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K20"/>
+  <dimension ref="B2:K20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="3" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
     <col width="46" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
     <col width="26" customWidth="1" min="6" max="6"/>
     <col width="30" customWidth="1" min="7" max="7"/>
-    <col width="33" customWidth="1" min="8" max="8"/>
-    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
     <col width="22" customWidth="1" min="10" max="10"/>
     <col width="40" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1"/>
-    <row r="2" ht="32" customHeight="1">
+    <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
           <t>Conference Sensitivity Set — 14 proceedings papers (CrossRef-verified; outside the 103-paper corpus)</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="8" customHeight="1"/>
-    <row r="4" ht="38" customHeight="1">
+    <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
           <t>#</t>
@@ -8595,7 +8591,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="54" customHeight="1">
+    <row r="5" ht="14" customHeight="1">
       <c r="B5" s="3" t="n">
         <v>1</v>
       </c>
@@ -8639,7 +8635,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="70" customHeight="1">
+    <row r="6" ht="14" customHeight="1">
       <c r="B6" s="6" t="n">
         <v>2</v>
       </c>
@@ -8683,7 +8679,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="54" customHeight="1">
+    <row r="7" ht="14" customHeight="1">
       <c r="B7" s="3" t="n">
         <v>3</v>
       </c>
@@ -8727,7 +8723,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="54" customHeight="1">
+    <row r="8" ht="14" customHeight="1">
       <c r="B8" s="6" t="n">
         <v>4</v>
       </c>
@@ -8771,7 +8767,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="54" customHeight="1">
+    <row r="9" ht="14" customHeight="1">
       <c r="B9" s="3" t="n">
         <v>5</v>
       </c>
@@ -8815,7 +8811,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="54" customHeight="1">
+    <row r="10" ht="14" customHeight="1">
       <c r="B10" s="6" t="n">
         <v>6</v>
       </c>
@@ -8859,7 +8855,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="38" customHeight="1">
+    <row r="11" ht="14" customHeight="1">
       <c r="B11" s="3" t="n">
         <v>7</v>
       </c>
@@ -8903,7 +8899,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="54" customHeight="1">
+    <row r="12" ht="14" customHeight="1">
       <c r="B12" s="6" t="n">
         <v>8</v>
       </c>
@@ -8947,7 +8943,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="54" customHeight="1">
+    <row r="13" ht="14" customHeight="1">
       <c r="B13" s="3" t="n">
         <v>9</v>
       </c>
@@ -8991,7 +8987,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="54" customHeight="1">
+    <row r="14" ht="14" customHeight="1">
       <c r="B14" s="6" t="n">
         <v>10</v>
       </c>
@@ -9035,7 +9031,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="54" customHeight="1">
+    <row r="15" ht="14" customHeight="1">
       <c r="B15" s="3" t="n">
         <v>11</v>
       </c>
@@ -9079,7 +9075,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="54" customHeight="1">
+    <row r="16" ht="14" customHeight="1">
       <c r="B16" s="6" t="n">
         <v>12</v>
       </c>
@@ -9123,7 +9119,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="54" customHeight="1">
+    <row r="17" ht="14" customHeight="1">
       <c r="B17" s="3" t="n">
         <v>13</v>
       </c>
@@ -9167,7 +9163,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="54" customHeight="1">
+    <row r="18" ht="14" customHeight="1">
       <c r="B18" s="6" t="n">
         <v>14</v>
       </c>
@@ -9220,9 +9216,8 @@
     </row>
   </sheetData>
   <autoFilter ref="B4:K18"/>
-  <mergeCells count="2">
+  <mergeCells count="1">
     <mergeCell ref="B20:I20"/>
-    <mergeCell ref="B2:K2"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId1"/>
